--- a/fullanime.xlsx
+++ b/fullanime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VoVanLinhTinh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D01B1B-898B-451C-A8CD-0E27A9D96606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3223A89-66C7-40B0-81D8-F975E2CA38DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12" yWindow="72" windowWidth="23028" windowHeight="12168" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="299">
   <si>
     <t>Netoge no Yome ga Ninki Idol datta</t>
   </si>
@@ -980,9 +980,6 @@
     <t>Hàng loạt người nhận được năng lực “Order” dựa trên điều ước của mình. Eiji khi còn nhỏ được hỏi về điều ước, cậu ước khiến thế giới bị phá hủy, dẫn đến thảm họa lớn. Eiji sống yên lặng, tránh sử dụng Order vì mặc cảm là người gây ra thảm họa. Cậu học ở trường bình thường, tiếp tục cuộc sống hàng ngày nhưng luôn bị bóng dáng quá khứ ám ảnh. Các người dùng Order khác bắt đầu xuất hiện, trong đó có Rin, người theo dõi và thử thách Eiji. Một số xung đột nhỏ xảy ra, Eiji buộc phải dùng sức mạnh để bảo vệ bản thân và người thân. Sena, chị gái của Eiji, bị cuốn vào âm mưu và nguy hiểm liên quan đến Order. Đây là động lực chính khiến Eiji phải ra tay và tham gia vào các sự kiện lớn. Eiji phát hiện ra các tổ chức, chính phủ và nhóm người dùng Order lợi dụng sức mạnh cho mục đích chính trị, chiến tranh. Các âm mưu dần lộ diện, cho thấy sức mạnh Order không chỉ cá nhân mà có thể thay đổi thế giới. Quá trình tìm hiểu hé lộ một số bí mật về Đại Phá Hủy, về cha mẹ Eiji, và về bản thân Eiji. Eiji nhận ra cậu có thể sử dụng Order để thay đổi tình hình hiện tại. Eiji tham gia trực tiếp các trận chiến chống lại những người dùng Order xấu và các mối nguy hiểm khác, phải lựa chọn giữa việc dùng sức mạnh để hủy diệt hay bảo vệ người thân. Eiji bảo vệ được người thân, đối mặt với hậu quả của điều ước và nhận ra rằng sức mạnh đi kèm trách nhiệm, và hành động hôm nay quyết định tương lai.</t>
   </si>
   <si>
-    <t>Hiraku Machio sau thời gian dài bệnh nặng chết đi, được một vị thần ban cho cơ hội sống lại và chuyển sinh sang một thế giới khác để thực hiện mong muốn: làm nông và sống yên bình. Khi tới thế giới mới, Hiraku được trao nông cụ toàn năng bởi thần, và được đặt vào khu rừng đầy quái vật để bắt đầu đời sống nông nghiệp từ con số không. Hiraku khai hoang, chặt cây, cày đất, trồng cây; quá trình này giúp anh dần mở rộng đất đai và năng lực sống sót trong môi trường khắc nghiệt. Dần dần, nhiều loài và chủng tộc khác (vampire, elf, thiên thần, rồng…) đến sống chung hoặc gia nhập “ngôi làng” mà Hiraku hình thành, khiến nông trại của anh mở rộng thành một cộng đồng. Ngôi làng phát triển thêm các cơ cấu: những người mới nhập cư, tổ chức công việc, tương tác giữa các chủng tộc và Hiraku ngày càng trở thành “người đứng đầu” hay “làng trưởng” trong cộng đồng đó. Câu chuyện tiếp diễn với các thử thách: từ việc bảo vệ nông trại, thiết lập quan hệ giữa các thành viên, mở rộng sản xuất, cho đến việc phát triển khu đất thành một nơi ổn định, hòa nhập giữa các chủng tộc khác nhau.</t>
-  </si>
-  <si>
     <t>Gojo Wakana, một nam sinh trung học thích làm búp bê Hina (búp bê truyền thống Nhật Bản), sống kín đáo, ít bạn vì sở thích “khác người” khiến cậu từng bị chê cười khi còn nhỏ. Kitagawa Marin, cô bạn cùng lớp yêu thích cosplay. Một ngày, Marin tình cờ phát hiện Gojo biết may vá và làm quần áo khi cậu đang sử dụng máy khâu ở phòng học. Marin nhờ Gojo giúp làm trang phục cosplay. Gojo dốc sức may bộ trang phục đầu tiên cho Marin. Khi Marin mặc thử và tham gia sự kiện cosplay, cả hai trở nên thân thiết hơn. Marin tiếp tục nhờ Gojo làm các bộ đồ cho nhiều nhân vật khác nhau. Qua mỗi lần chuẩn bị, họ hiểu nhau hơn và dần nảy sinh tình cảm. Gojo bắt đầu nhận ra tình cảm của mình dành cho Marin, còn Marin thì nhận thấy cô rung động trước sự tận tâm và chân thành của Gojo. Nhiều tình huống đời thường xen kẽ: đi mua vải, đi sự kiện cosplay, chụp ảnh, và những khoảnh khắc gần gũi khiến cả hai xấu hổ. Marin và Gojo cùng trải qua mùa hè, họ đi xem pháo hoa, nói chuyện về ước mơ, công việc và tương lai. Marin thể hiện rõ tình cảm của mình, còn Gojo dần mở lòng hơn về bản thân.</t>
   </si>
   <si>
@@ -1206,6 +1203,24 @@
   </si>
   <si>
     <t>Shijou Saikyou no Daimaou, Murabito A ni Tensei suru</t>
+  </si>
+  <si>
+    <t>Nanbaka</t>
+  </si>
+  <si>
+    <t>Zero no Tsukaima</t>
+  </si>
+  <si>
+    <t>0002_IsekaiNonbiriNouka.md</t>
+  </si>
+  <si>
+    <t>Fate/stay night: Unlimited Blade Works</t>
+  </si>
+  <si>
+    <t>Tomo-chan wa Onnanoko</t>
+  </si>
+  <si>
+    <t>Kanan-sama wa Akumade Choroi</t>
   </si>
 </sst>
 </file>
@@ -1863,24 +1878,24 @@
         <v>69</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D1" s="14"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:5" ht="159.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>227</v>
+      <c r="C2" s="22" t="s">
+        <v>295</v>
       </c>
       <c r="D2" s="14"/>
       <c r="E2" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -1891,11 +1906,11 @@
         <v>4</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="160.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1906,11 +1921,11 @@
         <v>5</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="222" customHeight="1" x14ac:dyDescent="0.3">
@@ -1921,11 +1936,11 @@
         <v>6</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="227.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1936,11 +1951,11 @@
         <v>7</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="288.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1951,11 +1966,11 @@
         <v>11</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="255" customHeight="1" x14ac:dyDescent="0.3">
@@ -1966,11 +1981,11 @@
         <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="149.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1985,7 +2000,7 @@
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="162" customHeight="1" x14ac:dyDescent="0.3">
@@ -2000,7 +2015,7 @@
       </c>
       <c r="D10" s="14"/>
       <c r="E10" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="147.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2011,11 +2026,11 @@
         <v>12</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="164.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2026,11 +2041,11 @@
         <v>13</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="146.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2045,7 +2060,7 @@
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="163.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2060,7 +2075,7 @@
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="101.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2075,7 +2090,7 @@
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.3">
@@ -2090,7 +2105,7 @@
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.3">
@@ -2105,7 +2120,7 @@
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="116.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2120,7 +2135,7 @@
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="143.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2135,7 +2150,7 @@
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="111" customHeight="1" x14ac:dyDescent="0.3">
@@ -2150,7 +2165,7 @@
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="131.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2165,7 +2180,7 @@
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2180,7 +2195,7 @@
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="83.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2195,7 +2210,7 @@
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.3">
@@ -2210,7 +2225,7 @@
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="98.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2225,7 +2240,7 @@
       </c>
       <c r="D25" s="18"/>
       <c r="E25" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="98.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2240,7 +2255,7 @@
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="83.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2255,7 +2270,7 @@
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="84" customHeight="1" x14ac:dyDescent="0.3">
@@ -2270,7 +2285,7 @@
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2285,7 +2300,7 @@
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="97.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2300,7 +2315,7 @@
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2315,7 +2330,7 @@
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="98.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2330,7 +2345,7 @@
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2345,7 +2360,7 @@
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2360,7 +2375,7 @@
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2375,7 +2390,7 @@
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2390,7 +2405,7 @@
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="84" customHeight="1" x14ac:dyDescent="0.3">
@@ -2405,7 +2420,7 @@
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="81.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2420,7 +2435,7 @@
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="83.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2435,7 +2450,7 @@
       </c>
       <c r="D39" s="18"/>
       <c r="E39" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.3">
@@ -2450,7 +2465,7 @@
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
@@ -2465,7 +2480,7 @@
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2480,7 +2495,7 @@
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2495,7 +2510,7 @@
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2510,7 +2525,7 @@
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="81.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2525,7 +2540,7 @@
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2540,7 +2555,7 @@
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2555,7 +2570,7 @@
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="83.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2570,7 +2585,7 @@
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2585,7 +2600,7 @@
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="83.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2600,7 +2615,7 @@
       </c>
       <c r="D50" s="14"/>
       <c r="E50" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.3">
@@ -2615,7 +2630,7 @@
       </c>
       <c r="D51" s="14"/>
       <c r="E51" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2630,7 +2645,7 @@
       </c>
       <c r="D52" s="14"/>
       <c r="E52" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2645,7 +2660,7 @@
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2660,7 +2675,7 @@
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="88.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2675,7 +2690,7 @@
       </c>
       <c r="D55" s="14"/>
       <c r="E55" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="83.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2690,7 +2705,7 @@
       </c>
       <c r="D56" s="18"/>
       <c r="E56" s="21" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2705,7 +2720,7 @@
       </c>
       <c r="D57" s="14"/>
       <c r="E57" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2720,7 +2735,7 @@
       </c>
       <c r="D58" s="18"/>
       <c r="E58" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2735,7 +2750,7 @@
       </c>
       <c r="D59" s="14"/>
       <c r="E59" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2750,7 +2765,7 @@
       </c>
       <c r="D60" s="14"/>
       <c r="E60" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2765,7 +2780,7 @@
       </c>
       <c r="D61" s="14"/>
       <c r="E61" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2780,7 +2795,7 @@
       </c>
       <c r="D62" s="14"/>
       <c r="E62" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.3">
@@ -2795,7 +2810,7 @@
       </c>
       <c r="D63" s="14"/>
       <c r="E63" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="72.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2810,7 +2825,7 @@
       </c>
       <c r="D64" s="14"/>
       <c r="E64" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2825,7 +2840,7 @@
       </c>
       <c r="D65" s="14"/>
       <c r="E65" s="21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2840,7 +2855,7 @@
       </c>
       <c r="D66" s="14"/>
       <c r="E66" s="21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="81.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2855,7 +2870,7 @@
       </c>
       <c r="D67" s="14"/>
       <c r="E67" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2870,7 +2885,7 @@
       </c>
       <c r="D68" s="14"/>
       <c r="E68" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2885,7 +2900,7 @@
       </c>
       <c r="D69" s="14"/>
       <c r="E69" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2900,7 +2915,7 @@
       </c>
       <c r="D70" s="14"/>
       <c r="E70" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -2913,7 +2928,7 @@
       <c r="C71" s="12"/>
       <c r="D71" s="14"/>
       <c r="E71" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2928,7 +2943,7 @@
       </c>
       <c r="D72" s="14"/>
       <c r="E72" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2943,7 +2958,7 @@
       </c>
       <c r="D73" s="14"/>
       <c r="E73" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2958,7 +2973,7 @@
       </c>
       <c r="D74" s="14"/>
       <c r="E74" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2973,7 +2988,7 @@
       </c>
       <c r="D75" s="14"/>
       <c r="E75" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="160.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2984,11 +2999,11 @@
         <v>219</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D76" s="14"/>
       <c r="E76" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="171.6" x14ac:dyDescent="0.3">
@@ -2999,11 +3014,11 @@
         <v>150</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D77" s="14"/>
       <c r="E77" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="195" customHeight="1" x14ac:dyDescent="0.3">
@@ -3018,7 +3033,7 @@
       </c>
       <c r="D78" s="14"/>
       <c r="E78" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="149.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3035,7 +3050,7 @@
         <v>213</v>
       </c>
       <c r="E79" s="21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
@@ -3047,10 +3062,10 @@
       </c>
       <c r="C80" s="12"/>
       <c r="D80" s="19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E80" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3063,7 +3078,7 @@
       <c r="C81" s="12"/>
       <c r="D81" s="14"/>
       <c r="E81" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
@@ -3075,10 +3090,10 @@
       </c>
       <c r="C82" s="12"/>
       <c r="D82" s="19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E82" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="234" x14ac:dyDescent="0.3">
@@ -3089,11 +3104,11 @@
         <v>154</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D83" s="14"/>
       <c r="E83" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3106,7 +3121,7 @@
       <c r="C84" s="12"/>
       <c r="D84" s="14"/>
       <c r="E84" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3119,7 +3134,7 @@
       <c r="C85" s="12"/>
       <c r="D85" s="14"/>
       <c r="E85" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="176.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3130,11 +3145,11 @@
         <v>157</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D86" s="14"/>
       <c r="E86" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3147,7 +3162,7 @@
       <c r="C87" s="12"/>
       <c r="D87" s="14"/>
       <c r="E87" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3160,7 +3175,7 @@
       <c r="C88" s="12"/>
       <c r="D88" s="14"/>
       <c r="E88" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -3173,7 +3188,7 @@
       <c r="C89" s="12"/>
       <c r="D89" s="14"/>
       <c r="E89" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3186,7 +3201,7 @@
       <c r="C90" s="12"/>
       <c r="D90" s="14"/>
       <c r="E90" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -3199,7 +3214,7 @@
       <c r="C91" s="12"/>
       <c r="D91" s="14"/>
       <c r="E91" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="117" customHeight="1" x14ac:dyDescent="0.3">
@@ -3214,7 +3229,7 @@
       </c>
       <c r="D92" s="14"/>
       <c r="E92" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="109.2" x14ac:dyDescent="0.3">
@@ -3229,7 +3244,7 @@
       </c>
       <c r="D93" s="14"/>
       <c r="E93" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3242,7 +3257,7 @@
       <c r="C94" s="12"/>
       <c r="D94" s="14"/>
       <c r="E94" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="124.8" x14ac:dyDescent="0.3">
@@ -3253,11 +3268,11 @@
         <v>164</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D95" s="14"/>
       <c r="E95" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="124.8" x14ac:dyDescent="0.3">
@@ -3268,11 +3283,11 @@
         <v>165</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D96" s="14"/>
       <c r="E96" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3285,7 +3300,7 @@
       <c r="C97" s="12"/>
       <c r="D97" s="14"/>
       <c r="E97" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3298,7 +3313,7 @@
       <c r="C98" s="12"/>
       <c r="D98" s="14"/>
       <c r="E98" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3311,7 +3326,7 @@
       <c r="C99" s="12"/>
       <c r="D99" s="14"/>
       <c r="E99" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3324,7 +3339,7 @@
       <c r="C100" s="12"/>
       <c r="D100" s="14"/>
       <c r="E100" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3337,7 +3352,7 @@
       <c r="C101" s="12"/>
       <c r="D101" s="14"/>
       <c r="E101" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -3350,7 +3365,7 @@
       <c r="C102" s="12"/>
       <c r="D102" s="14"/>
       <c r="E102" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3363,7 +3378,7 @@
       <c r="C103" s="12"/>
       <c r="D103" s="14"/>
       <c r="E103" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3376,7 +3391,7 @@
       <c r="C104" s="12"/>
       <c r="D104" s="14"/>
       <c r="E104" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3389,7 +3404,7 @@
       <c r="C105" s="12"/>
       <c r="D105" s="14"/>
       <c r="E105" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3402,7 +3417,7 @@
       <c r="C106" s="12"/>
       <c r="D106" s="14"/>
       <c r="E106" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3415,7 +3430,7 @@
       <c r="C107" s="12"/>
       <c r="D107" s="14"/>
       <c r="E107" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3428,7 +3443,7 @@
       <c r="C108" s="12"/>
       <c r="D108" s="18"/>
       <c r="E108" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3441,7 +3456,7 @@
       <c r="C109" s="12"/>
       <c r="D109" s="14"/>
       <c r="E109" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3454,7 +3469,7 @@
       <c r="C110" s="12"/>
       <c r="D110" s="14"/>
       <c r="E110" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3467,7 +3482,7 @@
       <c r="C111" s="12"/>
       <c r="D111" s="14"/>
       <c r="E111" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3480,7 +3495,7 @@
       <c r="C112" s="12"/>
       <c r="D112" s="14"/>
       <c r="E112" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -3493,7 +3508,7 @@
       <c r="C113" s="12"/>
       <c r="D113" s="14"/>
       <c r="E113" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3506,7 +3521,7 @@
       <c r="C114" s="12"/>
       <c r="D114" s="14"/>
       <c r="E114" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="195" customHeight="1" x14ac:dyDescent="0.3">
@@ -3517,11 +3532,11 @@
         <v>182</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D115" s="18"/>
       <c r="E115" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3534,7 +3549,7 @@
       <c r="C116" s="12"/>
       <c r="D116" s="14"/>
       <c r="E116" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3547,7 +3562,7 @@
       <c r="C117" s="12"/>
       <c r="D117" s="14"/>
       <c r="E117" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3560,7 +3575,7 @@
       <c r="C118" s="12"/>
       <c r="D118" s="14"/>
       <c r="E118" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3573,7 +3588,7 @@
       <c r="C119" s="12"/>
       <c r="D119" s="14"/>
       <c r="E119" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3586,7 +3601,7 @@
       <c r="C120" s="12"/>
       <c r="D120" s="14"/>
       <c r="E120" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3599,7 +3614,7 @@
       <c r="C121" s="12"/>
       <c r="D121" s="14"/>
       <c r="E121" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3612,7 +3627,7 @@
       <c r="C122" s="12"/>
       <c r="D122" s="14"/>
       <c r="E122" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3625,7 +3640,7 @@
       <c r="C123" s="12"/>
       <c r="D123" s="14"/>
       <c r="E123" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3638,7 +3653,7 @@
       <c r="C124" s="12"/>
       <c r="D124" s="14"/>
       <c r="E124" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="161.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3653,7 +3668,7 @@
       </c>
       <c r="D125" s="14"/>
       <c r="E125" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="165.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3670,7 +3685,7 @@
         <v>210</v>
       </c>
       <c r="E126" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="97.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3685,7 +3700,7 @@
       </c>
       <c r="D127" s="14"/>
       <c r="E127" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -3698,7 +3713,7 @@
       <c r="C128" s="12"/>
       <c r="D128" s="14"/>
       <c r="E128" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -3711,7 +3726,7 @@
       <c r="C129" s="12"/>
       <c r="D129" s="14"/>
       <c r="E129" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="109.2" x14ac:dyDescent="0.3">
@@ -3726,7 +3741,7 @@
       </c>
       <c r="D130" s="14"/>
       <c r="E130" s="21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -3739,7 +3754,7 @@
       <c r="C131" s="12"/>
       <c r="D131" s="14"/>
       <c r="E131" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="225" customHeight="1" x14ac:dyDescent="0.3">
@@ -3756,7 +3771,7 @@
         <v>215</v>
       </c>
       <c r="E132" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3769,7 +3784,7 @@
       <c r="C133" s="12"/>
       <c r="D133" s="14"/>
       <c r="E133" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="192.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3784,7 +3799,7 @@
       </c>
       <c r="D134" s="14"/>
       <c r="E134" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="180" customHeight="1" x14ac:dyDescent="0.3">
@@ -3801,7 +3816,7 @@
         <v>212</v>
       </c>
       <c r="E135" s="21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -3814,7 +3829,7 @@
       <c r="C136" s="12"/>
       <c r="D136" s="14"/>
       <c r="E136" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3827,7 +3842,7 @@
       <c r="C137" s="12"/>
       <c r="D137" s="14"/>
       <c r="E137" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3840,7 +3855,7 @@
       <c r="C138" s="12"/>
       <c r="D138" s="14"/>
       <c r="E138" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3853,7 +3868,7 @@
       <c r="C139" s="12"/>
       <c r="D139" s="14"/>
       <c r="E139" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3866,7 +3881,7 @@
       <c r="C140" s="12"/>
       <c r="D140" s="14"/>
       <c r="E140" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3879,7 +3894,7 @@
       <c r="C141" s="12"/>
       <c r="D141" s="14"/>
       <c r="E141" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -3892,7 +3907,7 @@
       <c r="C142" s="12"/>
       <c r="D142" s="14"/>
       <c r="E142" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3905,7 +3920,7 @@
       <c r="C143" s="12"/>
       <c r="D143" s="14"/>
       <c r="E143" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -3918,7 +3933,7 @@
       <c r="C144" s="12"/>
       <c r="D144" s="14"/>
       <c r="E144" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -3931,7 +3946,7 @@
       <c r="C145" s="12"/>
       <c r="D145" s="14"/>
       <c r="E145" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="199.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3939,14 +3954,14 @@
         <v>2</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C146" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D146" s="14"/>
       <c r="E146" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -3954,12 +3969,12 @@
         <v>68</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C147" s="12"/>
       <c r="D147" s="14"/>
       <c r="E147" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -3967,12 +3982,12 @@
         <v>68</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C148" s="12"/>
       <c r="D148" s="14"/>
       <c r="E148" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -3980,12 +3995,12 @@
         <v>68</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C149" s="12"/>
       <c r="D149" s="14"/>
       <c r="E149" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -3993,12 +4008,12 @@
         <v>68</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C150" s="12"/>
       <c r="D150" s="14"/>
       <c r="E150" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4006,12 +4021,12 @@
         <v>68</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C151" s="12"/>
       <c r="D151" s="14"/>
       <c r="E151" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4019,12 +4034,12 @@
         <v>68</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C152" s="12"/>
       <c r="D152" s="14"/>
       <c r="E152" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
@@ -4032,12 +4047,12 @@
         <v>68</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C153" s="12"/>
       <c r="D153" s="14"/>
       <c r="E153" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4045,12 +4060,12 @@
         <v>68</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C154" s="12"/>
       <c r="D154" s="14"/>
       <c r="E154" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4058,12 +4073,12 @@
         <v>68</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C155" s="12"/>
       <c r="D155" s="14"/>
       <c r="E155" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="177" customHeight="1" x14ac:dyDescent="0.3">
@@ -4071,14 +4086,14 @@
         <v>1</v>
       </c>
       <c r="B156" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="C156" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="D156" s="14"/>
       <c r="E156" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4086,12 +4101,12 @@
         <v>68</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C157" s="12"/>
       <c r="D157" s="18"/>
       <c r="E157" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
@@ -4099,12 +4114,12 @@
         <v>68</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C158" s="12"/>
       <c r="D158" s="14"/>
       <c r="E158" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4112,12 +4127,12 @@
         <v>68</v>
       </c>
       <c r="B159" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C159" s="12"/>
       <c r="D159" s="14"/>
       <c r="E159" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4125,12 +4140,12 @@
         <v>68</v>
       </c>
       <c r="B160" s="17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C160" s="12"/>
       <c r="D160" s="14"/>
       <c r="E160" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4138,12 +4153,12 @@
         <v>68</v>
       </c>
       <c r="B161" s="17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C161" s="12"/>
       <c r="D161" s="14"/>
       <c r="E161" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4151,12 +4166,12 @@
         <v>68</v>
       </c>
       <c r="B162" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C162" s="12"/>
       <c r="D162" s="14"/>
       <c r="E162" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4164,12 +4179,12 @@
         <v>68</v>
       </c>
       <c r="B163" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C163" s="12"/>
       <c r="D163" s="14"/>
       <c r="E163" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4177,12 +4192,12 @@
         <v>68</v>
       </c>
       <c r="B164" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C164" s="12"/>
       <c r="D164" s="14"/>
       <c r="E164" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
@@ -4190,12 +4205,12 @@
         <v>68</v>
       </c>
       <c r="B165" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C165" s="12"/>
       <c r="D165" s="14"/>
       <c r="E165" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4203,12 +4218,12 @@
         <v>68</v>
       </c>
       <c r="B166" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C166" s="12"/>
       <c r="D166" s="14"/>
       <c r="E166" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4216,12 +4231,12 @@
         <v>68</v>
       </c>
       <c r="B167" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C167" s="12"/>
       <c r="D167" s="14"/>
       <c r="E167" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4229,12 +4244,12 @@
         <v>68</v>
       </c>
       <c r="B168" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C168" s="12"/>
       <c r="D168" s="18"/>
       <c r="E168" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4242,12 +4257,12 @@
         <v>68</v>
       </c>
       <c r="B169" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C169" s="12"/>
       <c r="D169" s="18"/>
       <c r="E169" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4255,12 +4270,12 @@
         <v>68</v>
       </c>
       <c r="B170" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C170" s="12"/>
       <c r="D170" s="18"/>
       <c r="E170" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -4268,12 +4283,12 @@
         <v>2</v>
       </c>
       <c r="B171" s="17" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C171" s="12"/>
       <c r="D171" s="14"/>
       <c r="E171" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -4281,12 +4296,12 @@
         <v>1</v>
       </c>
       <c r="B172" s="17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C172" s="12"/>
       <c r="D172" s="14"/>
       <c r="E172" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
@@ -4294,12 +4309,12 @@
         <v>2</v>
       </c>
       <c r="B173" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C173" s="12"/>
       <c r="D173" s="14"/>
       <c r="E173" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
@@ -4307,12 +4322,12 @@
         <v>2</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C174" s="12"/>
       <c r="D174" s="14"/>
       <c r="E174" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
@@ -4320,12 +4335,12 @@
         <v>2</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C175" s="12"/>
       <c r="D175" s="14"/>
       <c r="E175" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
@@ -4333,12 +4348,12 @@
         <v>2</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C176" s="12"/>
       <c r="D176" s="14"/>
       <c r="E176" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
@@ -4346,12 +4361,12 @@
         <v>2</v>
       </c>
       <c r="B177" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C177" s="12"/>
       <c r="D177" s="14"/>
       <c r="E177" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
@@ -4359,12 +4374,12 @@
         <v>2</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C178" s="12"/>
       <c r="D178" s="14"/>
       <c r="E178" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4375,11 +4390,11 @@
         <v>149</v>
       </c>
       <c r="C179" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D179" s="14"/>
       <c r="E179" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
@@ -4387,12 +4402,12 @@
         <v>2</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C180" s="12"/>
       <c r="D180" s="14"/>
       <c r="E180" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
@@ -4400,67 +4415,77 @@
         <v>1</v>
       </c>
       <c r="B181" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C181" s="12"/>
       <c r="D181" s="14"/>
       <c r="E181" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B182" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="B182" s="13" t="s">
+        <v>293</v>
+      </c>
       <c r="C182" s="12"/>
       <c r="D182" s="14"/>
       <c r="E182" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B183" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="B183" s="13" t="s">
+        <v>294</v>
+      </c>
       <c r="C183" s="12"/>
       <c r="D183" s="14"/>
       <c r="E183" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B184" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="B184" s="13" t="s">
+        <v>296</v>
+      </c>
       <c r="C184" s="12"/>
       <c r="D184" s="14"/>
       <c r="E184" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B185" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="B185" s="13" t="s">
+        <v>297</v>
+      </c>
       <c r="C185" s="12"/>
       <c r="D185" s="14"/>
       <c r="E185" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B186" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="B186" s="13" t="s">
+        <v>298</v>
+      </c>
       <c r="C186" s="12"/>
       <c r="D186" s="14"/>
       <c r="E186" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
@@ -4471,7 +4496,7 @@
       <c r="C187" s="12"/>
       <c r="D187" s="14"/>
       <c r="E187" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
@@ -4482,7 +4507,7 @@
       <c r="C188" s="12"/>
       <c r="D188" s="14"/>
       <c r="E188" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
@@ -4493,7 +4518,7 @@
       <c r="C189" s="12"/>
       <c r="D189" s="14"/>
       <c r="E189" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
@@ -4504,7 +4529,7 @@
       <c r="C190" s="12"/>
       <c r="D190" s="14"/>
       <c r="E190" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
@@ -4515,7 +4540,7 @@
       <c r="C191" s="12"/>
       <c r="D191" s="14"/>
       <c r="E191" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
@@ -4526,7 +4551,7 @@
       <c r="C192" s="12"/>
       <c r="D192" s="14"/>
       <c r="E192" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
@@ -4537,7 +4562,7 @@
       <c r="C193" s="12"/>
       <c r="D193" s="14"/>
       <c r="E193" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
@@ -4548,7 +4573,7 @@
       <c r="C194" s="12"/>
       <c r="D194" s="14"/>
       <c r="E194" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
@@ -4559,7 +4584,7 @@
       <c r="C195" s="12"/>
       <c r="D195" s="14"/>
       <c r="E195" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
@@ -4570,7 +4595,7 @@
       <c r="C196" s="12"/>
       <c r="D196" s="14"/>
       <c r="E196" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
@@ -4581,7 +4606,7 @@
       <c r="C197" s="12"/>
       <c r="D197" s="14"/>
       <c r="E197" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
@@ -4592,7 +4617,7 @@
       <c r="C198" s="12"/>
       <c r="D198" s="14"/>
       <c r="E198" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
@@ -4603,7 +4628,7 @@
       <c r="C199" s="12"/>
       <c r="D199" s="14"/>
       <c r="E199" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
@@ -4614,7 +4639,7 @@
       <c r="C200" s="12"/>
       <c r="D200" s="14"/>
       <c r="E200" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
@@ -4625,7 +4650,7 @@
       <c r="C201" s="12"/>
       <c r="D201" s="14"/>
       <c r="E201" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
@@ -4636,7 +4661,7 @@
       <c r="C202" s="12"/>
       <c r="D202" s="14"/>
       <c r="E202" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
@@ -4647,7 +4672,7 @@
       <c r="C203" s="12"/>
       <c r="D203" s="14"/>
       <c r="E203" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
@@ -4658,7 +4683,7 @@
       <c r="C204" s="12"/>
       <c r="D204" s="14"/>
       <c r="E204" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
@@ -4669,7 +4694,7 @@
       <c r="C205" s="12"/>
       <c r="D205" s="14"/>
       <c r="E205" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
@@ -4680,7 +4705,7 @@
       <c r="C206" s="12"/>
       <c r="D206" s="14"/>
       <c r="E206" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
@@ -4691,7 +4716,7 @@
       <c r="C207" s="12"/>
       <c r="D207" s="14"/>
       <c r="E207" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
@@ -4702,7 +4727,7 @@
       <c r="C208" s="12"/>
       <c r="D208" s="14"/>
       <c r="E208" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
@@ -4713,7 +4738,7 @@
       <c r="C209" s="12"/>
       <c r="D209" s="14"/>
       <c r="E209" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
@@ -4724,7 +4749,7 @@
       <c r="C210" s="12"/>
       <c r="D210" s="14"/>
       <c r="E210" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
@@ -4735,7 +4760,7 @@
       <c r="C211" s="12"/>
       <c r="D211" s="14"/>
       <c r="E211" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
@@ -4746,7 +4771,7 @@
       <c r="C212" s="12"/>
       <c r="D212" s="14"/>
       <c r="E212" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
@@ -4757,7 +4782,7 @@
       <c r="C213" s="12"/>
       <c r="D213" s="14"/>
       <c r="E213" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
@@ -4768,7 +4793,7 @@
       <c r="C214" s="12"/>
       <c r="D214" s="14"/>
       <c r="E214" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
@@ -4779,7 +4804,7 @@
       <c r="C215" s="12"/>
       <c r="D215" s="14"/>
       <c r="E215" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
@@ -4790,7 +4815,7 @@
       <c r="C216" s="12"/>
       <c r="D216" s="14"/>
       <c r="E216" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
@@ -4801,7 +4826,7 @@
       <c r="C217" s="12"/>
       <c r="D217" s="14"/>
       <c r="E217" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
@@ -4812,7 +4837,7 @@
       <c r="C218" s="12"/>
       <c r="D218" s="14"/>
       <c r="E218" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
@@ -4823,7 +4848,7 @@
       <c r="C219" s="12"/>
       <c r="D219" s="14"/>
       <c r="E219" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
@@ -4834,7 +4859,7 @@
       <c r="C220" s="12"/>
       <c r="D220" s="14"/>
       <c r="E220" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
@@ -4845,7 +4870,7 @@
       <c r="C221" s="12"/>
       <c r="D221" s="14"/>
       <c r="E221" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
@@ -4856,7 +4881,7 @@
       <c r="C222" s="12"/>
       <c r="D222" s="14"/>
       <c r="E222" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
@@ -4867,7 +4892,7 @@
       <c r="C223" s="12"/>
       <c r="D223" s="14"/>
       <c r="E223" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
@@ -4878,7 +4903,7 @@
       <c r="C224" s="12"/>
       <c r="D224" s="14"/>
       <c r="E224" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
@@ -4889,7 +4914,7 @@
       <c r="C225" s="12"/>
       <c r="D225" s="14"/>
       <c r="E225" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
@@ -4900,7 +4925,7 @@
       <c r="C226" s="12"/>
       <c r="D226" s="14"/>
       <c r="E226" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
@@ -4911,7 +4936,7 @@
       <c r="C227" s="12"/>
       <c r="D227" s="14"/>
       <c r="E227" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
@@ -4922,7 +4947,7 @@
       <c r="C228" s="12"/>
       <c r="D228" s="14"/>
       <c r="E228" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
@@ -4933,7 +4958,7 @@
       <c r="C229" s="12"/>
       <c r="D229" s="14"/>
       <c r="E229" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
@@ -4944,7 +4969,7 @@
       <c r="C230" s="12"/>
       <c r="D230" s="14"/>
       <c r="E230" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
@@ -4955,7 +4980,7 @@
       <c r="C231" s="12"/>
       <c r="D231" s="14"/>
       <c r="E231" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
@@ -4966,7 +4991,7 @@
       <c r="C232" s="12"/>
       <c r="D232" s="14"/>
       <c r="E232" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
@@ -4977,7 +5002,7 @@
       <c r="C233" s="12"/>
       <c r="D233" s="14"/>
       <c r="E233" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
@@ -4988,7 +5013,7 @@
       <c r="C234" s="12"/>
       <c r="D234" s="14"/>
       <c r="E234" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
@@ -4999,7 +5024,7 @@
       <c r="C235" s="12"/>
       <c r="D235" s="14"/>
       <c r="E235" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
@@ -5010,7 +5035,7 @@
       <c r="C236" s="12"/>
       <c r="D236" s="14"/>
       <c r="E236" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
@@ -5021,7 +5046,7 @@
       <c r="C237" s="12"/>
       <c r="D237" s="14"/>
       <c r="E237" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
@@ -5032,7 +5057,7 @@
       <c r="C238" s="12"/>
       <c r="D238" s="14"/>
       <c r="E238" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
@@ -5043,7 +5068,7 @@
       <c r="C239" s="12"/>
       <c r="D239" s="14"/>
       <c r="E239" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
@@ -5054,7 +5079,7 @@
       <c r="C240" s="12"/>
       <c r="D240" s="14"/>
       <c r="E240" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.3">
@@ -5065,7 +5090,7 @@
       <c r="C241" s="12"/>
       <c r="D241" s="14"/>
       <c r="E241" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.3">
@@ -5076,7 +5101,7 @@
       <c r="C242" s="12"/>
       <c r="D242" s="14"/>
       <c r="E242" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.3">
@@ -5087,7 +5112,7 @@
       <c r="C243" s="12"/>
       <c r="D243" s="14"/>
       <c r="E243" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.3">
@@ -5098,7 +5123,7 @@
       <c r="C244" s="12"/>
       <c r="D244" s="14"/>
       <c r="E244" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.3">
@@ -5109,7 +5134,7 @@
       <c r="C245" s="12"/>
       <c r="D245" s="14"/>
       <c r="E245" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.3">
@@ -5120,7 +5145,7 @@
       <c r="C246" s="12"/>
       <c r="D246" s="14"/>
       <c r="E246" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.3">
@@ -5131,7 +5156,7 @@
       <c r="C247" s="12"/>
       <c r="D247" s="14"/>
       <c r="E247" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.3">
@@ -5142,7 +5167,7 @@
       <c r="C248" s="12"/>
       <c r="D248" s="14"/>
       <c r="E248" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.3">
@@ -5153,7 +5178,7 @@
       <c r="C249" s="12"/>
       <c r="D249" s="14"/>
       <c r="E249" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.3">
@@ -5164,7 +5189,7 @@
       <c r="C250" s="12"/>
       <c r="D250" s="14"/>
       <c r="E250" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.3">
@@ -5175,7 +5200,7 @@
       <c r="C251" s="12"/>
       <c r="D251" s="14"/>
       <c r="E251" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.3">
@@ -5186,7 +5211,7 @@
       <c r="C252" s="12"/>
       <c r="D252" s="14"/>
       <c r="E252" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
@@ -5197,7 +5222,7 @@
       <c r="C253" s="12"/>
       <c r="D253" s="14"/>
       <c r="E253" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
@@ -5208,7 +5233,7 @@
       <c r="C254" s="12"/>
       <c r="D254" s="14"/>
       <c r="E254" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.3">
@@ -5219,7 +5244,7 @@
       <c r="C255" s="12"/>
       <c r="D255" s="14"/>
       <c r="E255" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
@@ -5230,7 +5255,7 @@
       <c r="C256" s="12"/>
       <c r="D256" s="14"/>
       <c r="E256" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
@@ -5241,7 +5266,7 @@
       <c r="C257" s="12"/>
       <c r="D257" s="14"/>
       <c r="E257" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.3">
@@ -5252,7 +5277,7 @@
       <c r="C258" s="12"/>
       <c r="D258" s="14"/>
       <c r="E258" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
@@ -5263,7 +5288,7 @@
       <c r="C259" s="12"/>
       <c r="D259" s="14"/>
       <c r="E259" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
@@ -5274,7 +5299,7 @@
       <c r="C260" s="12"/>
       <c r="D260" s="14"/>
       <c r="E260" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
@@ -5285,7 +5310,7 @@
       <c r="C261" s="12"/>
       <c r="D261" s="14"/>
       <c r="E261" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
@@ -5296,7 +5321,7 @@
       <c r="C262" s="12"/>
       <c r="D262" s="14"/>
       <c r="E262" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
@@ -5307,7 +5332,7 @@
       <c r="C263" s="12"/>
       <c r="D263" s="14"/>
       <c r="E263" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
@@ -5318,7 +5343,7 @@
       <c r="C264" s="12"/>
       <c r="D264" s="14"/>
       <c r="E264" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
@@ -5329,7 +5354,7 @@
       <c r="C265" s="12"/>
       <c r="D265" s="14"/>
       <c r="E265" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
@@ -5340,7 +5365,7 @@
       <c r="C266" s="12"/>
       <c r="D266" s="14"/>
       <c r="E266" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
@@ -5351,7 +5376,7 @@
       <c r="C267" s="12"/>
       <c r="D267" s="14"/>
       <c r="E267" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
@@ -5362,7 +5387,7 @@
       <c r="C268" s="12"/>
       <c r="D268" s="14"/>
       <c r="E268" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
@@ -5373,7 +5398,7 @@
       <c r="C269" s="12"/>
       <c r="D269" s="14"/>
       <c r="E269" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
@@ -5384,7 +5409,7 @@
       <c r="C270" s="12"/>
       <c r="D270" s="14"/>
       <c r="E270" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.3">
@@ -5395,7 +5420,7 @@
       <c r="C271" s="12"/>
       <c r="D271" s="14"/>
       <c r="E271" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
@@ -5406,7 +5431,7 @@
       <c r="C272" s="12"/>
       <c r="D272" s="14"/>
       <c r="E272" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.3">
@@ -5417,7 +5442,7 @@
       <c r="C273" s="12"/>
       <c r="D273" s="14"/>
       <c r="E273" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.3">
@@ -5428,7 +5453,7 @@
       <c r="C274" s="12"/>
       <c r="D274" s="14"/>
       <c r="E274" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
@@ -5439,7 +5464,7 @@
       <c r="C275" s="12"/>
       <c r="D275" s="14"/>
       <c r="E275" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
@@ -5450,7 +5475,7 @@
       <c r="C276" s="12"/>
       <c r="D276" s="14"/>
       <c r="E276" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.3">
@@ -5461,7 +5486,7 @@
       <c r="C277" s="12"/>
       <c r="D277" s="14"/>
       <c r="E277" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.3">
@@ -5472,7 +5497,7 @@
       <c r="C278" s="12"/>
       <c r="D278" s="14"/>
       <c r="E278" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.3">
@@ -5483,7 +5508,7 @@
       <c r="C279" s="12"/>
       <c r="D279" s="14"/>
       <c r="E279" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.3">
@@ -5494,7 +5519,7 @@
       <c r="C280" s="12"/>
       <c r="D280" s="14"/>
       <c r="E280" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.3">
@@ -5505,7 +5530,7 @@
       <c r="C281" s="12"/>
       <c r="D281" s="14"/>
       <c r="E281" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.3">
@@ -5516,7 +5541,7 @@
       <c r="C282" s="12"/>
       <c r="D282" s="14"/>
       <c r="E282" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.3">
@@ -5527,7 +5552,7 @@
       <c r="C283" s="12"/>
       <c r="D283" s="14"/>
       <c r="E283" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.3">
@@ -5538,7 +5563,7 @@
       <c r="C284" s="12"/>
       <c r="D284" s="14"/>
       <c r="E284" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.3">
@@ -5549,7 +5574,7 @@
       <c r="C285" s="12"/>
       <c r="D285" s="14"/>
       <c r="E285" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.3">
@@ -5560,7 +5585,7 @@
       <c r="C286" s="12"/>
       <c r="D286" s="14"/>
       <c r="E286" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.3">
@@ -5571,7 +5596,7 @@
       <c r="C287" s="12"/>
       <c r="D287" s="14"/>
       <c r="E287" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.3">
@@ -5582,7 +5607,7 @@
       <c r="C288" s="12"/>
       <c r="D288" s="14"/>
       <c r="E288" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.3">
@@ -5593,7 +5618,7 @@
       <c r="C289" s="12"/>
       <c r="D289" s="14"/>
       <c r="E289" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.3">
@@ -5604,7 +5629,7 @@
       <c r="C290" s="12"/>
       <c r="D290" s="14"/>
       <c r="E290" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.3">
@@ -5615,7 +5640,7 @@
       <c r="C291" s="12"/>
       <c r="D291" s="14"/>
       <c r="E291" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.3">
@@ -5626,7 +5651,7 @@
       <c r="C292" s="12"/>
       <c r="D292" s="14"/>
       <c r="E292" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.3">
@@ -5637,7 +5662,7 @@
       <c r="C293" s="12"/>
       <c r="D293" s="14"/>
       <c r="E293" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.3">
@@ -5648,7 +5673,7 @@
       <c r="C294" s="12"/>
       <c r="D294" s="14"/>
       <c r="E294" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.3">
@@ -5659,7 +5684,7 @@
       <c r="C295" s="12"/>
       <c r="D295" s="14"/>
       <c r="E295" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.3">
@@ -5670,7 +5695,7 @@
       <c r="C296" s="12"/>
       <c r="D296" s="14"/>
       <c r="E296" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.3">
@@ -5681,7 +5706,7 @@
       <c r="C297" s="12"/>
       <c r="D297" s="14"/>
       <c r="E297" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.3">
@@ -5692,7 +5717,7 @@
       <c r="C298" s="12"/>
       <c r="D298" s="14"/>
       <c r="E298" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.3">
@@ -5703,7 +5728,7 @@
       <c r="C299" s="12"/>
       <c r="D299" s="14"/>
       <c r="E299" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.3">
@@ -5714,7 +5739,7 @@
       <c r="C300" s="12"/>
       <c r="D300" s="14"/>
       <c r="E300" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.3">
@@ -5725,7 +5750,7 @@
       <c r="C301" s="12"/>
       <c r="D301" s="14"/>
       <c r="E301" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.3">
@@ -5736,7 +5761,7 @@
       <c r="C302" s="12"/>
       <c r="D302" s="14"/>
       <c r="E302" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.3">
@@ -5747,7 +5772,7 @@
       <c r="C303" s="12"/>
       <c r="D303" s="14"/>
       <c r="E303" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.3">
@@ -5758,7 +5783,7 @@
       <c r="C304" s="12"/>
       <c r="D304" s="14"/>
       <c r="E304" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.3">
@@ -5769,7 +5794,7 @@
       <c r="C305" s="12"/>
       <c r="D305" s="14"/>
       <c r="E305" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.3">
@@ -5780,7 +5805,7 @@
       <c r="C306" s="12"/>
       <c r="D306" s="14"/>
       <c r="E306" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.3">
@@ -5791,7 +5816,7 @@
       <c r="C307" s="12"/>
       <c r="D307" s="14"/>
       <c r="E307" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.3">
@@ -5802,7 +5827,7 @@
       <c r="C308" s="12"/>
       <c r="D308" s="14"/>
       <c r="E308" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.3">
@@ -5813,7 +5838,7 @@
       <c r="C309" s="12"/>
       <c r="D309" s="14"/>
       <c r="E309" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.3">
@@ -5824,7 +5849,7 @@
       <c r="C310" s="12"/>
       <c r="D310" s="14"/>
       <c r="E310" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.3">
@@ -5835,7 +5860,7 @@
       <c r="C311" s="12"/>
       <c r="D311" s="14"/>
       <c r="E311" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.3">
@@ -5846,7 +5871,7 @@
       <c r="C312" s="12"/>
       <c r="D312" s="14"/>
       <c r="E312" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.3">
@@ -5857,7 +5882,7 @@
       <c r="C313" s="12"/>
       <c r="D313" s="14"/>
       <c r="E313" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.3">
@@ -5868,7 +5893,7 @@
       <c r="C314" s="12"/>
       <c r="D314" s="14"/>
       <c r="E314" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.3">
@@ -5879,7 +5904,7 @@
       <c r="C315" s="12"/>
       <c r="D315" s="14"/>
       <c r="E315" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.3">
@@ -5890,7 +5915,7 @@
       <c r="C316" s="12"/>
       <c r="D316" s="14"/>
       <c r="E316" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.3">
@@ -5901,7 +5926,7 @@
       <c r="C317" s="12"/>
       <c r="D317" s="14"/>
       <c r="E317" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.3">
@@ -5912,7 +5937,7 @@
       <c r="C318" s="12"/>
       <c r="D318" s="14"/>
       <c r="E318" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.3">
@@ -5923,7 +5948,7 @@
       <c r="C319" s="12"/>
       <c r="D319" s="14"/>
       <c r="E319" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.3">
@@ -5934,7 +5959,7 @@
       <c r="C320" s="12"/>
       <c r="D320" s="14"/>
       <c r="E320" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.3">
@@ -5945,7 +5970,7 @@
       <c r="C321" s="12"/>
       <c r="D321" s="14"/>
       <c r="E321" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.3">
@@ -5956,7 +5981,7 @@
       <c r="C322" s="12"/>
       <c r="D322" s="14"/>
       <c r="E322" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.3">
@@ -5967,7 +5992,7 @@
       <c r="C323" s="12"/>
       <c r="D323" s="14"/>
       <c r="E323" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.3">
@@ -5978,7 +6003,7 @@
       <c r="C324" s="12"/>
       <c r="D324" s="14"/>
       <c r="E324" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.3">
@@ -5989,7 +6014,7 @@
       <c r="C325" s="12"/>
       <c r="D325" s="14"/>
       <c r="E325" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.3">
@@ -6000,7 +6025,7 @@
       <c r="C326" s="12"/>
       <c r="D326" s="14"/>
       <c r="E326" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.3">
@@ -6011,7 +6036,7 @@
       <c r="C327" s="12"/>
       <c r="D327" s="14"/>
       <c r="E327" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.3">
@@ -6022,7 +6047,7 @@
       <c r="C328" s="12"/>
       <c r="D328" s="14"/>
       <c r="E328" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.3">
@@ -6033,7 +6058,7 @@
       <c r="C329" s="12"/>
       <c r="D329" s="14"/>
       <c r="E329" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.3">
@@ -6044,7 +6069,7 @@
       <c r="C330" s="12"/>
       <c r="D330" s="14"/>
       <c r="E330" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.3">
@@ -6055,7 +6080,7 @@
       <c r="C331" s="12"/>
       <c r="D331" s="14"/>
       <c r="E331" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.3">
@@ -6066,7 +6091,7 @@
       <c r="C332" s="12"/>
       <c r="D332" s="14"/>
       <c r="E332" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.3">
@@ -6077,7 +6102,7 @@
       <c r="C333" s="12"/>
       <c r="D333" s="14"/>
       <c r="E333" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.3">
@@ -6088,7 +6113,7 @@
       <c r="C334" s="12"/>
       <c r="D334" s="14"/>
       <c r="E334" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.3">
@@ -6099,7 +6124,7 @@
       <c r="C335" s="12"/>
       <c r="D335" s="14"/>
       <c r="E335" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.3">
@@ -6110,7 +6135,7 @@
       <c r="C336" s="12"/>
       <c r="D336" s="14"/>
       <c r="E336" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.3">
@@ -6121,7 +6146,7 @@
       <c r="C337" s="12"/>
       <c r="D337" s="14"/>
       <c r="E337" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.3">
@@ -6132,7 +6157,7 @@
       <c r="C338" s="12"/>
       <c r="D338" s="14"/>
       <c r="E338" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.3">
@@ -6143,7 +6168,7 @@
       <c r="C339" s="12"/>
       <c r="D339" s="14"/>
       <c r="E339" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.3">
@@ -6154,7 +6179,7 @@
       <c r="C340" s="12"/>
       <c r="D340" s="14"/>
       <c r="E340" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.3">
@@ -6165,7 +6190,7 @@
       <c r="C341" s="12"/>
       <c r="D341" s="14"/>
       <c r="E341" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.3">
@@ -6176,7 +6201,7 @@
       <c r="C342" s="12"/>
       <c r="D342" s="14"/>
       <c r="E342" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.3">
@@ -6187,7 +6212,7 @@
       <c r="C343" s="12"/>
       <c r="D343" s="14"/>
       <c r="E343" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.3">
@@ -6198,7 +6223,7 @@
       <c r="C344" s="12"/>
       <c r="D344" s="14"/>
       <c r="E344" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.3">
@@ -6209,7 +6234,7 @@
       <c r="C345" s="12"/>
       <c r="D345" s="14"/>
       <c r="E345" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.3">
@@ -6220,7 +6245,7 @@
       <c r="C346" s="12"/>
       <c r="D346" s="14"/>
       <c r="E346" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.3">
@@ -6231,7 +6256,7 @@
       <c r="C347" s="12"/>
       <c r="D347" s="14"/>
       <c r="E347" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.3">
@@ -6242,7 +6267,7 @@
       <c r="C348" s="12"/>
       <c r="D348" s="14"/>
       <c r="E348" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.3">
@@ -6253,7 +6278,7 @@
       <c r="C349" s="12"/>
       <c r="D349" s="14"/>
       <c r="E349" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.3">
@@ -6264,7 +6289,7 @@
       <c r="C350" s="12"/>
       <c r="D350" s="14"/>
       <c r="E350" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.3">
@@ -6275,7 +6300,7 @@
       <c r="C351" s="12"/>
       <c r="D351" s="14"/>
       <c r="E351" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.3">
@@ -6286,7 +6311,7 @@
       <c r="C352" s="12"/>
       <c r="D352" s="14"/>
       <c r="E352" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.3">
@@ -6297,7 +6322,7 @@
       <c r="C353" s="12"/>
       <c r="D353" s="14"/>
       <c r="E353" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.3">
@@ -6308,7 +6333,7 @@
       <c r="C354" s="12"/>
       <c r="D354" s="14"/>
       <c r="E354" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.3">
@@ -6319,7 +6344,7 @@
       <c r="C355" s="12"/>
       <c r="D355" s="14"/>
       <c r="E355" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.3">
@@ -6330,7 +6355,7 @@
       <c r="C356" s="12"/>
       <c r="D356" s="14"/>
       <c r="E356" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.3">
@@ -6341,7 +6366,7 @@
       <c r="C357" s="12"/>
       <c r="D357" s="14"/>
       <c r="E357" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.3">
@@ -6352,7 +6377,7 @@
       <c r="C358" s="12"/>
       <c r="D358" s="14"/>
       <c r="E358" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.3">
@@ -6363,7 +6388,7 @@
       <c r="C359" s="12"/>
       <c r="D359" s="14"/>
       <c r="E359" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.3">
@@ -6374,7 +6399,7 @@
       <c r="C360" s="12"/>
       <c r="D360" s="14"/>
       <c r="E360" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.3">
@@ -6385,7 +6410,7 @@
       <c r="C361" s="12"/>
       <c r="D361" s="14"/>
       <c r="E361" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.3">
@@ -6396,7 +6421,7 @@
       <c r="C362" s="12"/>
       <c r="D362" s="14"/>
       <c r="E362" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.3">
@@ -6407,7 +6432,7 @@
       <c r="C363" s="12"/>
       <c r="D363" s="14"/>
       <c r="E363" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.3">
@@ -6418,7 +6443,7 @@
       <c r="C364" s="12"/>
       <c r="D364" s="14"/>
       <c r="E364" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.3">
@@ -6429,7 +6454,7 @@
       <c r="C365" s="12"/>
       <c r="D365" s="14"/>
       <c r="E365" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.3">
@@ -6440,7 +6465,7 @@
       <c r="C366" s="12"/>
       <c r="D366" s="14"/>
       <c r="E366" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.3">
@@ -6451,7 +6476,7 @@
       <c r="C367" s="12"/>
       <c r="D367" s="14"/>
       <c r="E367" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.3">
@@ -6462,7 +6487,7 @@
       <c r="C368" s="12"/>
       <c r="D368" s="14"/>
       <c r="E368" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.3">
@@ -6473,7 +6498,7 @@
       <c r="C369" s="12"/>
       <c r="D369" s="14"/>
       <c r="E369" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.3">
@@ -6484,7 +6509,7 @@
       <c r="C370" s="12"/>
       <c r="D370" s="14"/>
       <c r="E370" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.3">
@@ -6495,7 +6520,7 @@
       <c r="C371" s="12"/>
       <c r="D371" s="14"/>
       <c r="E371" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.3">
@@ -6506,7 +6531,7 @@
       <c r="C372" s="12"/>
       <c r="D372" s="14"/>
       <c r="E372" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.3">
@@ -6517,7 +6542,7 @@
       <c r="C373" s="12"/>
       <c r="D373" s="14"/>
       <c r="E373" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.3">
@@ -6528,7 +6553,7 @@
       <c r="C374" s="12"/>
       <c r="D374" s="14"/>
       <c r="E374" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.3">
@@ -6539,7 +6564,7 @@
       <c r="C375" s="12"/>
       <c r="D375" s="14"/>
       <c r="E375" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.3">
@@ -6550,7 +6575,7 @@
       <c r="C376" s="12"/>
       <c r="D376" s="14"/>
       <c r="E376" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.3">
@@ -6561,7 +6586,7 @@
       <c r="C377" s="12"/>
       <c r="D377" s="14"/>
       <c r="E377" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.3">
@@ -6572,7 +6597,7 @@
       <c r="C378" s="12"/>
       <c r="D378" s="14"/>
       <c r="E378" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.3">
@@ -6583,7 +6608,7 @@
       <c r="C379" s="12"/>
       <c r="D379" s="14"/>
       <c r="E379" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.3">
@@ -6594,7 +6619,7 @@
       <c r="C380" s="12"/>
       <c r="D380" s="14"/>
       <c r="E380" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.3">
@@ -6605,7 +6630,7 @@
       <c r="C381" s="12"/>
       <c r="D381" s="14"/>
       <c r="E381" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.3">
@@ -6616,7 +6641,7 @@
       <c r="C382" s="12"/>
       <c r="D382" s="14"/>
       <c r="E382" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.3">
@@ -6627,7 +6652,7 @@
       <c r="C383" s="12"/>
       <c r="D383" s="14"/>
       <c r="E383" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.3">
@@ -6638,7 +6663,7 @@
       <c r="C384" s="12"/>
       <c r="D384" s="14"/>
       <c r="E384" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.3">
@@ -6649,7 +6674,7 @@
       <c r="C385" s="12"/>
       <c r="D385" s="14"/>
       <c r="E385" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.3">
@@ -6660,7 +6685,7 @@
       <c r="C386" s="12"/>
       <c r="D386" s="14"/>
       <c r="E386" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.3">
@@ -6671,7 +6696,7 @@
       <c r="C387" s="12"/>
       <c r="D387" s="14"/>
       <c r="E387" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.3">
@@ -6682,7 +6707,7 @@
       <c r="C388" s="12"/>
       <c r="D388" s="14"/>
       <c r="E388" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.3">
@@ -6693,7 +6718,7 @@
       <c r="C389" s="12"/>
       <c r="D389" s="14"/>
       <c r="E389" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.3">
@@ -6704,7 +6729,7 @@
       <c r="C390" s="12"/>
       <c r="D390" s="14"/>
       <c r="E390" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.3">
@@ -6715,7 +6740,7 @@
       <c r="C391" s="12"/>
       <c r="D391" s="14"/>
       <c r="E391" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.3">
@@ -6726,7 +6751,7 @@
       <c r="C392" s="12"/>
       <c r="D392" s="14"/>
       <c r="E392" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.3">
@@ -6737,7 +6762,7 @@
       <c r="C393" s="12"/>
       <c r="D393" s="14"/>
       <c r="E393" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.3">
@@ -6748,7 +6773,7 @@
       <c r="C394" s="12"/>
       <c r="D394" s="14"/>
       <c r="E394" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.3">
@@ -6759,7 +6784,7 @@
       <c r="C395" s="12"/>
       <c r="D395" s="14"/>
       <c r="E395" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.3">
@@ -6770,7 +6795,7 @@
       <c r="C396" s="12"/>
       <c r="D396" s="14"/>
       <c r="E396" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.3">
@@ -6781,7 +6806,7 @@
       <c r="C397" s="12"/>
       <c r="D397" s="14"/>
       <c r="E397" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.3">
@@ -6792,7 +6817,7 @@
       <c r="C398" s="12"/>
       <c r="D398" s="14"/>
       <c r="E398" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.3">
@@ -6803,7 +6828,7 @@
       <c r="C399" s="12"/>
       <c r="D399" s="14"/>
       <c r="E399" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.3">
@@ -6814,7 +6839,7 @@
       <c r="C400" s="12"/>
       <c r="D400" s="14"/>
       <c r="E400" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.3">
@@ -6825,7 +6850,7 @@
       <c r="C401" s="12"/>
       <c r="D401" s="14"/>
       <c r="E401" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.3">
@@ -6836,7 +6861,7 @@
       <c r="C402" s="12"/>
       <c r="D402" s="14"/>
       <c r="E402" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.3">
@@ -6847,7 +6872,7 @@
       <c r="C403" s="12"/>
       <c r="D403" s="14"/>
       <c r="E403" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.3">
@@ -6858,7 +6883,7 @@
       <c r="C404" s="12"/>
       <c r="D404" s="14"/>
       <c r="E404" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.3">
@@ -6869,7 +6894,7 @@
       <c r="C405" s="12"/>
       <c r="D405" s="14"/>
       <c r="E405" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.3">
@@ -6880,7 +6905,7 @@
       <c r="C406" s="12"/>
       <c r="D406" s="14"/>
       <c r="E406" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.3">
@@ -6891,7 +6916,7 @@
       <c r="C407" s="12"/>
       <c r="D407" s="14"/>
       <c r="E407" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.3">
@@ -6902,7 +6927,7 @@
       <c r="C408" s="12"/>
       <c r="D408" s="14"/>
       <c r="E408" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.3">
@@ -6913,7 +6938,7 @@
       <c r="C409" s="12"/>
       <c r="D409" s="14"/>
       <c r="E409" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.3">
@@ -6924,7 +6949,7 @@
       <c r="C410" s="12"/>
       <c r="D410" s="14"/>
       <c r="E410" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.3">
@@ -6935,7 +6960,7 @@
       <c r="C411" s="12"/>
       <c r="D411" s="14"/>
       <c r="E411" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.3">
@@ -6946,7 +6971,7 @@
       <c r="C412" s="12"/>
       <c r="D412" s="14"/>
       <c r="E412" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.3">
@@ -6957,7 +6982,7 @@
       <c r="C413" s="12"/>
       <c r="D413" s="14"/>
       <c r="E413" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.3">
@@ -6968,7 +6993,7 @@
       <c r="C414" s="12"/>
       <c r="D414" s="14"/>
       <c r="E414" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.3">
@@ -6979,7 +7004,7 @@
       <c r="C415" s="12"/>
       <c r="D415" s="14"/>
       <c r="E415" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.3">
@@ -6990,7 +7015,7 @@
       <c r="C416" s="12"/>
       <c r="D416" s="14"/>
       <c r="E416" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.3">
@@ -7001,7 +7026,7 @@
       <c r="C417" s="12"/>
       <c r="D417" s="14"/>
       <c r="E417" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.3">
@@ -7012,7 +7037,7 @@
       <c r="C418" s="12"/>
       <c r="D418" s="14"/>
       <c r="E418" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.3">
@@ -7023,7 +7048,7 @@
       <c r="C419" s="12"/>
       <c r="D419" s="14"/>
       <c r="E419" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.3">
@@ -7034,7 +7059,7 @@
       <c r="C420" s="12"/>
       <c r="D420" s="14"/>
       <c r="E420" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.3">
@@ -7045,7 +7070,7 @@
       <c r="C421" s="12"/>
       <c r="D421" s="14"/>
       <c r="E421" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.3">
@@ -7056,7 +7081,7 @@
       <c r="C422" s="12"/>
       <c r="D422" s="14"/>
       <c r="E422" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.3">
@@ -7067,7 +7092,7 @@
       <c r="C423" s="12"/>
       <c r="D423" s="14"/>
       <c r="E423" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.3">
@@ -7078,7 +7103,7 @@
       <c r="C424" s="12"/>
       <c r="D424" s="14"/>
       <c r="E424" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.3">
@@ -7089,7 +7114,7 @@
       <c r="C425" s="12"/>
       <c r="D425" s="14"/>
       <c r="E425" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.3">
@@ -7100,7 +7125,7 @@
       <c r="C426" s="12"/>
       <c r="D426" s="14"/>
       <c r="E426" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.3">
@@ -7111,7 +7136,7 @@
       <c r="C427" s="12"/>
       <c r="D427" s="14"/>
       <c r="E427" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.3">
@@ -7122,7 +7147,7 @@
       <c r="C428" s="12"/>
       <c r="D428" s="14"/>
       <c r="E428" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.3">
@@ -7133,7 +7158,7 @@
       <c r="C429" s="12"/>
       <c r="D429" s="14"/>
       <c r="E429" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.3">
@@ -7144,7 +7169,7 @@
       <c r="C430" s="12"/>
       <c r="D430" s="14"/>
       <c r="E430" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.3">
@@ -7155,7 +7180,7 @@
       <c r="C431" s="12"/>
       <c r="D431" s="14"/>
       <c r="E431" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.3">
@@ -7166,7 +7191,7 @@
       <c r="C432" s="12"/>
       <c r="D432" s="14"/>
       <c r="E432" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.3">
@@ -7177,7 +7202,7 @@
       <c r="C433" s="12"/>
       <c r="D433" s="14"/>
       <c r="E433" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.3">
@@ -7188,7 +7213,7 @@
       <c r="C434" s="12"/>
       <c r="D434" s="14"/>
       <c r="E434" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.3">
@@ -7199,7 +7224,7 @@
       <c r="C435" s="12"/>
       <c r="D435" s="14"/>
       <c r="E435" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.3">
@@ -7210,7 +7235,7 @@
       <c r="C436" s="12"/>
       <c r="D436" s="14"/>
       <c r="E436" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.3">
@@ -7221,7 +7246,7 @@
       <c r="C437" s="12"/>
       <c r="D437" s="14"/>
       <c r="E437" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.3">
@@ -7232,7 +7257,7 @@
       <c r="C438" s="12"/>
       <c r="D438" s="14"/>
       <c r="E438" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.3">
@@ -7243,7 +7268,7 @@
       <c r="C439" s="12"/>
       <c r="D439" s="14"/>
       <c r="E439" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.3">
@@ -7254,7 +7279,7 @@
       <c r="C440" s="12"/>
       <c r="D440" s="14"/>
       <c r="E440" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.3">
@@ -7265,7 +7290,7 @@
       <c r="C441" s="12"/>
       <c r="D441" s="14"/>
       <c r="E441" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.3">
@@ -7276,7 +7301,7 @@
       <c r="C442" s="12"/>
       <c r="D442" s="14"/>
       <c r="E442" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.3">
@@ -7287,7 +7312,7 @@
       <c r="C443" s="12"/>
       <c r="D443" s="14"/>
       <c r="E443" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.3">
@@ -7298,7 +7323,7 @@
       <c r="C444" s="12"/>
       <c r="D444" s="14"/>
       <c r="E444" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.3">
@@ -7309,7 +7334,7 @@
       <c r="C445" s="12"/>
       <c r="D445" s="14"/>
       <c r="E445" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.3">
@@ -7320,7 +7345,7 @@
       <c r="C446" s="12"/>
       <c r="D446" s="14"/>
       <c r="E446" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.3">
@@ -7331,7 +7356,7 @@
       <c r="C447" s="12"/>
       <c r="D447" s="14"/>
       <c r="E447" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.3">
@@ -7342,7 +7367,7 @@
       <c r="C448" s="12"/>
       <c r="D448" s="14"/>
       <c r="E448" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.3">
@@ -7353,7 +7378,7 @@
       <c r="C449" s="12"/>
       <c r="D449" s="14"/>
       <c r="E449" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.3">
@@ -7364,7 +7389,7 @@
       <c r="C450" s="12"/>
       <c r="D450" s="14"/>
       <c r="E450" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.3">
@@ -7375,7 +7400,7 @@
       <c r="C451" s="12"/>
       <c r="D451" s="14"/>
       <c r="E451" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.3">
@@ -7386,7 +7411,7 @@
       <c r="C452" s="12"/>
       <c r="D452" s="14"/>
       <c r="E452" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.3">
@@ -7397,7 +7422,7 @@
       <c r="C453" s="12"/>
       <c r="D453" s="14"/>
       <c r="E453" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.3">
@@ -7408,7 +7433,7 @@
       <c r="C454" s="12"/>
       <c r="D454" s="14"/>
       <c r="E454" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.3">
@@ -7419,7 +7444,7 @@
       <c r="C455" s="12"/>
       <c r="D455" s="14"/>
       <c r="E455" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.3">
@@ -7430,7 +7455,7 @@
       <c r="C456" s="12"/>
       <c r="D456" s="14"/>
       <c r="E456" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.3">
@@ -7441,7 +7466,7 @@
       <c r="C457" s="12"/>
       <c r="D457" s="14"/>
       <c r="E457" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.3">
@@ -7452,7 +7477,7 @@
       <c r="C458" s="12"/>
       <c r="D458" s="14"/>
       <c r="E458" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.3">
@@ -7463,7 +7488,7 @@
       <c r="C459" s="12"/>
       <c r="D459" s="14"/>
       <c r="E459" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.3">
@@ -7474,7 +7499,7 @@
       <c r="C460" s="12"/>
       <c r="D460" s="14"/>
       <c r="E460" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.3">
@@ -7485,7 +7510,7 @@
       <c r="C461" s="12"/>
       <c r="D461" s="14"/>
       <c r="E461" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.3">
@@ -7496,7 +7521,7 @@
       <c r="C462" s="12"/>
       <c r="D462" s="14"/>
       <c r="E462" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.3">
@@ -7507,7 +7532,7 @@
       <c r="C463" s="12"/>
       <c r="D463" s="14"/>
       <c r="E463" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.3">
@@ -7518,7 +7543,7 @@
       <c r="C464" s="12"/>
       <c r="D464" s="14"/>
       <c r="E464" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.3">
@@ -7529,7 +7554,7 @@
       <c r="C465" s="12"/>
       <c r="D465" s="14"/>
       <c r="E465" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.3">
@@ -7540,7 +7565,7 @@
       <c r="C466" s="12"/>
       <c r="D466" s="14"/>
       <c r="E466" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.3">
@@ -7551,7 +7576,7 @@
       <c r="C467" s="12"/>
       <c r="D467" s="14"/>
       <c r="E467" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.3">
@@ -7562,7 +7587,7 @@
       <c r="C468" s="12"/>
       <c r="D468" s="14"/>
       <c r="E468" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.3">
@@ -7573,7 +7598,7 @@
       <c r="C469" s="12"/>
       <c r="D469" s="14"/>
       <c r="E469" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.3">
@@ -7584,7 +7609,7 @@
       <c r="C470" s="12"/>
       <c r="D470" s="14"/>
       <c r="E470" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.3">
@@ -7595,7 +7620,7 @@
       <c r="C471" s="12"/>
       <c r="D471" s="14"/>
       <c r="E471" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.3">
@@ -7606,7 +7631,7 @@
       <c r="C472" s="12"/>
       <c r="D472" s="14"/>
       <c r="E472" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.3">
@@ -7617,7 +7642,7 @@
       <c r="C473" s="12"/>
       <c r="D473" s="14"/>
       <c r="E473" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.3">
@@ -7628,7 +7653,7 @@
       <c r="C474" s="12"/>
       <c r="D474" s="14"/>
       <c r="E474" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.3">
@@ -7639,7 +7664,7 @@
       <c r="C475" s="12"/>
       <c r="D475" s="14"/>
       <c r="E475" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.3">
@@ -7650,7 +7675,7 @@
       <c r="C476" s="12"/>
       <c r="D476" s="14"/>
       <c r="E476" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.3">
@@ -7661,7 +7686,7 @@
       <c r="C477" s="12"/>
       <c r="D477" s="14"/>
       <c r="E477" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.3">
@@ -7672,7 +7697,7 @@
       <c r="C478" s="12"/>
       <c r="D478" s="14"/>
       <c r="E478" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.3">
@@ -7683,7 +7708,7 @@
       <c r="C479" s="12"/>
       <c r="D479" s="14"/>
       <c r="E479" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.3">
@@ -7694,7 +7719,7 @@
       <c r="C480" s="12"/>
       <c r="D480" s="14"/>
       <c r="E480" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.3">
@@ -7705,7 +7730,7 @@
       <c r="C481" s="12"/>
       <c r="D481" s="14"/>
       <c r="E481" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.3">
@@ -7716,7 +7741,7 @@
       <c r="C482" s="12"/>
       <c r="D482" s="14"/>
       <c r="E482" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.3">
@@ -7727,7 +7752,7 @@
       <c r="C483" s="12"/>
       <c r="D483" s="14"/>
       <c r="E483" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.3">
@@ -7738,7 +7763,7 @@
       <c r="C484" s="12"/>
       <c r="D484" s="14"/>
       <c r="E484" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.3">
@@ -7749,7 +7774,7 @@
       <c r="C485" s="12"/>
       <c r="D485" s="14"/>
       <c r="E485" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.3">
@@ -7760,7 +7785,7 @@
       <c r="C486" s="12"/>
       <c r="D486" s="14"/>
       <c r="E486" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.3">
@@ -7771,7 +7796,7 @@
       <c r="C487" s="12"/>
       <c r="D487" s="14"/>
       <c r="E487" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.3">
@@ -7782,7 +7807,7 @@
       <c r="C488" s="12"/>
       <c r="D488" s="14"/>
       <c r="E488" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.3">
@@ -7793,7 +7818,7 @@
       <c r="C489" s="12"/>
       <c r="D489" s="14"/>
       <c r="E489" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.3">
@@ -7804,7 +7829,7 @@
       <c r="C490" s="12"/>
       <c r="D490" s="14"/>
       <c r="E490" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.3">
@@ -7815,7 +7840,7 @@
       <c r="C491" s="12"/>
       <c r="D491" s="14"/>
       <c r="E491" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.3">
@@ -7826,7 +7851,7 @@
       <c r="C492" s="12"/>
       <c r="D492" s="14"/>
       <c r="E492" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.3">
@@ -7837,7 +7862,7 @@
       <c r="C493" s="12"/>
       <c r="D493" s="14"/>
       <c r="E493" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.3">
@@ -7848,7 +7873,7 @@
       <c r="C494" s="12"/>
       <c r="D494" s="14"/>
       <c r="E494" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.3">
@@ -7859,7 +7884,7 @@
       <c r="C495" s="12"/>
       <c r="D495" s="14"/>
       <c r="E495" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -7892,9 +7917,10 @@
   <hyperlinks>
     <hyperlink ref="C179" r:id="rId1" xr:uid="{921E8A16-9E7A-4EAE-B2C2-A8EE538DE9DE}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{71D1475F-6C52-4F4B-8987-82ACEF7ECCBD}"/>
+    <hyperlink ref="C2" r:id="rId3" xr:uid="{C8121117-1C79-4CC9-AFBD-3F64FE8DAE83}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
-  <drawing r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>